--- a/space-battleship/config_excel/planet_build.xlsx
+++ b/space-battleship/config_excel/planet_build.xlsx
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>施工需额外船员，建成后可在此星球重铸一次。重铸将获得大量提升,并解锁新的星球.</t>
+          <t>首颗星球重铸准备：达到探索条件后，派遣额外船员建设新型船坞。建成后领取设施，再选择重铸；重铸保留现有资源与永久星球奖励。</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>施工需额外船员，建成后可在此星球重铸一次。重铸将获得大量提升,并解锁新的星球.</t>
+          <t>后续星球的新型船坞：达到探索条件并完成建设后可重铸。建成后领取设施，再选择重铸。</t>
         </is>
       </c>
       <c r="D8" t="n">

--- a/space-battleship/config_excel/planet_build.xlsx
+++ b/space-battleship/config_excel/planet_build.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后续星球的新型船坞：达到探索条件并完成建设后可重铸。建成后领取设施，再选择重铸。</t>
+          <t>首颗星球重铸准备：达到探索条件后，派遣额外船员建设新型船坞。建成后领取设施，再选择重铸；重铸保留现有资源与永久星球奖励。</t>
         </is>
       </c>
       <c r="D8" t="n">

--- a/space-battleship/config_excel/planet_build.xlsx
+++ b/space-battleship/config_excel/planet_build.xlsx
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>首颗星球重铸准备：达到探索条件后，派遣额外船员建设新型船坞。建成后领取设施，再选择重铸；重铸保留现有资源与永久星球奖励。</t>
+          <t>首颗星球重铸准备：达到探索条件后，派遣额外船员建设新型船坞。建成后领取设施，再选择重铸；重铸保留现有铁与铀余额与永久星球奖励。</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>首颗星球重铸准备：达到探索条件后，派遣额外船员建设新型船坞。建成后领取设施，再选择重铸；重铸保留现有资源与永久星球奖励。</t>
+          <t>首颗星球重铸准备：达到探索条件后，派遣额外船员建设新型船坞。建成后领取设施，再选择重铸；重铸保留现有铁与铀余额与永久星球奖励。</t>
         </is>
       </c>
       <c r="D8" t="n">

--- a/space-battleship/config_excel/planet_build.xlsx
+++ b/space-battleship/config_excel/planet_build.xlsx
@@ -1432,7 +1432,7 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
         <v>180</v>

--- a/space-battleship/config_excel/planet_build.xlsx
+++ b/space-battleship/config_excel/planet_build.xlsx
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>首颗星球重铸准备：达到探索条件后，派遣额外船员建设新型船坞。建成后领取设施，再选择重铸；重铸保留现有铁与铀余额与永久星球奖励。</t>
+          <t>点「分配施工船员」开工；建好后领取船坞，再决定是否重铸。重铸前会显示保留内容和本轮重置范围。</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>首颗星球重铸准备：达到探索条件后，派遣额外船员建设新型船坞。建成后领取设施，再选择重铸；重铸保留现有铁与铀余额与永久星球奖励。</t>
+          <t>点「分配施工船员」开工；建好后领取船坞，再决定是否重铸。重铸前会显示保留内容和本轮重置范围。</t>
         </is>
       </c>
       <c r="D8" t="n">
